--- a/public/data/final_clustered.xlsx
+++ b/public/data/final_clustered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Magang\Proyek KP\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E2580A-D533-40A0-A638-466A784BD82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D832D233-BB6B-4BE5-AA34-5B98A4B6BD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6098,9 +6098,6 @@
     <t>Jawa Tengah</t>
   </si>
   <si>
-    <t>Di Yogyakarta</t>
-  </si>
-  <si>
     <t>Jawa Barat</t>
   </si>
   <si>
@@ -6141,6 +6138,9 @@
   </si>
   <si>
     <t>PT Trimegah Selaras</t>
+  </si>
+  <si>
+    <t>DI Yogyakarta</t>
   </si>
 </sst>
 </file>
@@ -6697,7 +6697,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q2" t="s">
         <v>793</v>
@@ -6813,7 +6813,7 @@
         <v>4</v>
       </c>
       <c r="P3" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q3" t="s">
         <v>793</v>
@@ -6917,7 +6917,7 @@
         <v>4</v>
       </c>
       <c r="P4" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q4" t="s">
         <v>793</v>
@@ -7030,7 +7030,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q5" t="s">
         <v>793</v>
@@ -7143,7 +7143,7 @@
         <v>4</v>
       </c>
       <c r="P6" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q6" t="s">
         <v>794</v>
@@ -7256,7 +7256,7 @@
         <v>4</v>
       </c>
       <c r="P7" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q7" t="s">
         <v>794</v>
@@ -7360,7 +7360,7 @@
         <v>4</v>
       </c>
       <c r="P8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q8" t="s">
         <v>794</v>
@@ -7470,7 +7470,7 @@
         <v>4</v>
       </c>
       <c r="P9" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q9" t="s">
         <v>795</v>
@@ -7574,7 +7574,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q10" t="s">
         <v>796</v>
@@ -7678,7 +7678,7 @@
         <v>4</v>
       </c>
       <c r="P11" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q11" t="s">
         <v>796</v>
@@ -7782,7 +7782,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q12" t="s">
         <v>796</v>
@@ -7886,7 +7886,7 @@
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q13" t="s">
         <v>796</v>
@@ -7990,7 +7990,7 @@
         <v>4</v>
       </c>
       <c r="P14" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q14" t="s">
         <v>797</v>
@@ -8091,7 +8091,7 @@
         <v>4</v>
       </c>
       <c r="P15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q15" t="s">
         <v>797</v>
@@ -8195,7 +8195,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q16" t="s">
         <v>797</v>
@@ -8296,7 +8296,7 @@
         <v>4</v>
       </c>
       <c r="P17" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q17" t="s">
         <v>796</v>
@@ -8397,7 +8397,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q18" t="s">
         <v>796</v>
@@ -8498,7 +8498,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q19" t="s">
         <v>796</v>
@@ -8599,7 +8599,7 @@
         <v>4</v>
       </c>
       <c r="P20" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q20" t="s">
         <v>796</v>
@@ -8703,7 +8703,7 @@
         <v>4</v>
       </c>
       <c r="P21" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q21" t="s">
         <v>796</v>
@@ -8807,7 +8807,7 @@
         <v>4</v>
       </c>
       <c r="P22" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q22" t="s">
         <v>796</v>
@@ -8908,7 +8908,7 @@
         <v>4</v>
       </c>
       <c r="P23" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q23" t="s">
         <v>797</v>
@@ -9009,7 +9009,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q24" t="s">
         <v>796</v>
@@ -9113,7 +9113,7 @@
         <v>4</v>
       </c>
       <c r="P25" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q25" t="s">
         <v>793</v>
@@ -9229,7 +9229,7 @@
         <v>4</v>
       </c>
       <c r="P26" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q26" t="s">
         <v>793</v>
@@ -9333,7 +9333,7 @@
         <v>4</v>
       </c>
       <c r="P27" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q27" t="s">
         <v>796</v>
@@ -9437,7 +9437,7 @@
         <v>4</v>
       </c>
       <c r="P28" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q28" t="s">
         <v>796</v>
@@ -9538,7 +9538,7 @@
         <v>4</v>
       </c>
       <c r="P29" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q29" t="s">
         <v>796</v>
@@ -9642,7 +9642,7 @@
         <v>4</v>
       </c>
       <c r="P30" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q30" t="s">
         <v>797</v>
@@ -9743,7 +9743,7 @@
         <v>4</v>
       </c>
       <c r="P31" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q31" t="s">
         <v>797</v>
@@ -9844,7 +9844,7 @@
         <v>4</v>
       </c>
       <c r="P32" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q32" t="s">
         <v>793</v>
@@ -9948,7 +9948,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q33" t="s">
         <v>797</v>
@@ -10049,7 +10049,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q34" t="s">
         <v>798</v>
@@ -10153,7 +10153,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q35" t="s">
         <v>793</v>
@@ -10263,7 +10263,7 @@
         <v>4</v>
       </c>
       <c r="P36" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q36" t="s">
         <v>799</v>
@@ -10376,7 +10376,7 @@
         <v>4</v>
       </c>
       <c r="P37" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q37" t="s">
         <v>799</v>
@@ -10489,7 +10489,7 @@
         <v>4</v>
       </c>
       <c r="P38" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q38" t="s">
         <v>799</v>
@@ -10602,7 +10602,7 @@
         <v>4</v>
       </c>
       <c r="P39" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q39" t="s">
         <v>799</v>
@@ -10715,7 +10715,7 @@
         <v>4</v>
       </c>
       <c r="P40" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q40" t="s">
         <v>800</v>
@@ -10816,7 +10816,7 @@
         <v>4</v>
       </c>
       <c r="P41" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q41" t="s">
         <v>800</v>
@@ -10926,7 +10926,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q42" t="s">
         <v>799</v>
@@ -11039,7 +11039,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q43" t="s">
         <v>799</v>
@@ -11155,7 +11155,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q44" t="s">
         <v>799</v>
@@ -11268,7 +11268,7 @@
         <v>4</v>
       </c>
       <c r="P45" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q45" t="s">
         <v>799</v>
@@ -11378,7 +11378,7 @@
         <v>4</v>
       </c>
       <c r="P46" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q46" t="s">
         <v>799</v>
@@ -11494,7 +11494,7 @@
         <v>4</v>
       </c>
       <c r="P47" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q47" t="s">
         <v>799</v>
@@ -11610,7 +11610,7 @@
         <v>4</v>
       </c>
       <c r="P48" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q48" t="s">
         <v>800</v>
@@ -11723,7 +11723,7 @@
         <v>4</v>
       </c>
       <c r="P49" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q49" t="s">
         <v>800</v>
@@ -11836,7 +11836,7 @@
         <v>4</v>
       </c>
       <c r="P50" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q50" t="s">
         <v>801</v>
@@ -11949,7 +11949,7 @@
         <v>4</v>
       </c>
       <c r="P51" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q51" t="s">
         <v>801</v>
@@ -12050,7 +12050,7 @@
         <v>4</v>
       </c>
       <c r="P52" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q52" t="s">
         <v>801</v>
@@ -12166,7 +12166,7 @@
         <v>4</v>
       </c>
       <c r="P53" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q53" t="s">
         <v>794</v>
@@ -12282,7 +12282,7 @@
         <v>4</v>
       </c>
       <c r="P54" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q54" t="s">
         <v>794</v>
@@ -12383,7 +12383,7 @@
         <v>4</v>
       </c>
       <c r="P55" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q55" t="s">
         <v>794</v>
@@ -12481,7 +12481,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q56" t="s">
         <v>802</v>
@@ -12594,7 +12594,7 @@
         <v>4</v>
       </c>
       <c r="P57" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q57" t="s">
         <v>802</v>
@@ -12704,7 +12704,7 @@
         <v>4</v>
       </c>
       <c r="P58" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q58" t="s">
         <v>802</v>
@@ -12811,7 +12811,7 @@
         <v>4</v>
       </c>
       <c r="P59" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q59" t="s">
         <v>802</v>
@@ -12924,7 +12924,7 @@
         <v>4</v>
       </c>
       <c r="P60" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q60" t="s">
         <v>803</v>
@@ -13037,7 +13037,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q61" t="s">
         <v>803</v>
@@ -13150,7 +13150,7 @@
         <v>4</v>
       </c>
       <c r="P62" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q62" t="s">
         <v>802</v>
@@ -13266,7 +13266,7 @@
         <v>4</v>
       </c>
       <c r="P63" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q63" t="s">
         <v>802</v>
@@ -13382,7 +13382,7 @@
         <v>4</v>
       </c>
       <c r="P64" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q64" t="s">
         <v>802</v>
@@ -13495,7 +13495,7 @@
         <v>4</v>
       </c>
       <c r="P65" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q65" t="s">
         <v>803</v>
@@ -13608,7 +13608,7 @@
         <v>4</v>
       </c>
       <c r="P66" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q66" t="s">
         <v>803</v>
@@ -13718,7 +13718,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q67" t="s">
         <v>802</v>
@@ -13819,7 +13819,7 @@
         <v>4</v>
       </c>
       <c r="P68" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q68" t="s">
         <v>804</v>
@@ -13932,7 +13932,7 @@
         <v>4</v>
       </c>
       <c r="P69" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q69" t="s">
         <v>804</v>
@@ -14045,7 +14045,7 @@
         <v>4</v>
       </c>
       <c r="P70" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q70" t="s">
         <v>804</v>
@@ -14158,7 +14158,7 @@
         <v>4</v>
       </c>
       <c r="P71" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q71" t="s">
         <v>804</v>
@@ -14274,7 +14274,7 @@
         <v>4</v>
       </c>
       <c r="P72" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q72" t="s">
         <v>805</v>
@@ -14378,7 +14378,7 @@
         <v>4</v>
       </c>
       <c r="P73" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q73" t="s">
         <v>805</v>
@@ -14494,7 +14494,7 @@
         <v>4</v>
       </c>
       <c r="P74" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q74" t="s">
         <v>805</v>
@@ -14580,7 +14580,7 @@
         <v>759</v>
       </c>
       <c r="G75" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H75" t="s">
         <v>775</v>
@@ -14678,7 +14678,7 @@
         <v>759</v>
       </c>
       <c r="G76" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H76" t="s">
         <v>775</v>
@@ -14785,7 +14785,7 @@
         <v>759</v>
       </c>
       <c r="G77" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H77" t="s">
         <v>775</v>
@@ -14901,7 +14901,7 @@
         <v>759</v>
       </c>
       <c r="G78" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H78" t="s">
         <v>775</v>
@@ -15011,7 +15011,7 @@
         <v>759</v>
       </c>
       <c r="G79" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H79" t="s">
         <v>775</v>
@@ -15124,7 +15124,7 @@
         <v>759</v>
       </c>
       <c r="G80" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H80" t="s">
         <v>775</v>
@@ -15225,7 +15225,7 @@
         <v>760</v>
       </c>
       <c r="G81" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H81" t="s">
         <v>776</v>
@@ -15252,7 +15252,7 @@
         <v>4</v>
       </c>
       <c r="P81" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q81" t="s">
         <v>804</v>
@@ -15338,7 +15338,7 @@
         <v>760</v>
       </c>
       <c r="G82" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H82" t="s">
         <v>777</v>
@@ -15365,7 +15365,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q82" t="s">
         <v>804</v>
@@ -15451,7 +15451,7 @@
         <v>760</v>
       </c>
       <c r="G83" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H83" t="s">
         <v>778</v>
@@ -15478,7 +15478,7 @@
         <v>4</v>
       </c>
       <c r="P83" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="Q83" t="s">
         <v>804</v>
@@ -15564,7 +15564,7 @@
         <v>760</v>
       </c>
       <c r="G84" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H84" t="s">
         <v>777</v>
@@ -15591,7 +15591,7 @@
         <v>4</v>
       </c>
       <c r="P84" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q84" t="s">
         <v>805</v>
@@ -15677,7 +15677,7 @@
         <v>760</v>
       </c>
       <c r="G85" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H85" t="s">
         <v>777</v>
@@ -15704,7 +15704,7 @@
         <v>4</v>
       </c>
       <c r="P85" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q85" t="s">
         <v>805</v>
@@ -15790,7 +15790,7 @@
         <v>759</v>
       </c>
       <c r="G86" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H86" t="s">
         <v>775</v>
@@ -15900,7 +15900,7 @@
         <v>759</v>
       </c>
       <c r="G87" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H87" t="s">
         <v>775</v>
@@ -16010,7 +16010,7 @@
         <v>759</v>
       </c>
       <c r="G88" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H88" t="s">
         <v>775</v>
@@ -16120,7 +16120,7 @@
         <v>759</v>
       </c>
       <c r="G89" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H89" t="s">
         <v>775</v>
@@ -16233,7 +16233,7 @@
         <v>759</v>
       </c>
       <c r="G90" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H90" t="s">
         <v>775</v>
@@ -16343,7 +16343,7 @@
         <v>759</v>
       </c>
       <c r="G91" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H91" t="s">
         <v>775</v>
@@ -16438,7 +16438,7 @@
         <v>759</v>
       </c>
       <c r="G92" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H92" t="s">
         <v>775</v>
@@ -16551,7 +16551,7 @@
         <v>760</v>
       </c>
       <c r="G93" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H93" t="s">
         <v>778</v>
@@ -16578,7 +16578,7 @@
         <v>4</v>
       </c>
       <c r="P93" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="Q93" t="s">
         <v>805</v>
@@ -16652,7 +16652,7 @@
         <v>760</v>
       </c>
       <c r="G94" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H94" t="s">
         <v>778</v>
@@ -16679,7 +16679,7 @@
         <v>4</v>
       </c>
       <c r="P94" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="Q94" t="s">
         <v>805</v>
@@ -16768,7 +16768,7 @@
         <v>761</v>
       </c>
       <c r="G95" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H95" t="s">
         <v>779</v>
@@ -16795,7 +16795,7 @@
         <v>4</v>
       </c>
       <c r="P95" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="Q95" t="s">
         <v>805</v>
@@ -16881,7 +16881,7 @@
         <v>760</v>
       </c>
       <c r="G96" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H96" t="s">
         <v>777</v>
@@ -16908,7 +16908,7 @@
         <v>4</v>
       </c>
       <c r="P96" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q96" t="s">
         <v>804</v>
@@ -16988,7 +16988,7 @@
         <v>760</v>
       </c>
       <c r="G97" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H97" t="s">
         <v>777</v>
@@ -17015,7 +17015,7 @@
         <v>4</v>
       </c>
       <c r="P97" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q97" t="s">
         <v>805</v>
@@ -17086,7 +17086,7 @@
         <v>762</v>
       </c>
       <c r="G98" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H98" t="s">
         <v>772</v>
@@ -17113,7 +17113,7 @@
         <v>4</v>
       </c>
       <c r="P98" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q98" t="s">
         <v>806</v>
@@ -17190,7 +17190,7 @@
         <v>762</v>
       </c>
       <c r="G99" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H99" t="s">
         <v>780</v>
@@ -17217,7 +17217,7 @@
         <v>70</v>
       </c>
       <c r="P99" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="Q99" t="s">
         <v>807</v>
@@ -17303,7 +17303,7 @@
         <v>762</v>
       </c>
       <c r="G100" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H100" t="s">
         <v>772</v>
@@ -17330,7 +17330,7 @@
         <v>4</v>
       </c>
       <c r="P100" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q100" t="s">
         <v>806</v>
@@ -17413,7 +17413,7 @@
         <v>762</v>
       </c>
       <c r="G101" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H101" t="s">
         <v>781</v>
@@ -17520,7 +17520,7 @@
         <v>763</v>
       </c>
       <c r="G102" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H102" t="s">
         <v>782</v>
@@ -17547,7 +17547,7 @@
         <v>4</v>
       </c>
       <c r="P102" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q102" t="s">
         <v>808</v>
@@ -17633,7 +17633,7 @@
         <v>763</v>
       </c>
       <c r="G103" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H103" t="s">
         <v>778</v>
@@ -17660,7 +17660,7 @@
         <v>4</v>
       </c>
       <c r="P103" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q103" t="s">
         <v>808</v>
@@ -17731,7 +17731,7 @@
         <v>762</v>
       </c>
       <c r="G104" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H104" t="s">
         <v>775</v>
@@ -17841,7 +17841,7 @@
         <v>762</v>
       </c>
       <c r="G105" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="H105" t="s">
         <v>772</v>
@@ -17868,7 +17868,7 @@
         <v>4</v>
       </c>
       <c r="P105" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q105" t="s">
         <v>806</v>
@@ -17954,7 +17954,7 @@
         <v>763</v>
       </c>
       <c r="G106" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H106" t="s">
         <v>778</v>
@@ -17981,7 +17981,7 @@
         <v>4</v>
       </c>
       <c r="P106" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q106" t="s">
         <v>808</v>
@@ -18055,7 +18055,7 @@
         <v>763</v>
       </c>
       <c r="G107" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H107" t="s">
         <v>782</v>
@@ -18082,7 +18082,7 @@
         <v>4</v>
       </c>
       <c r="P107" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q107" t="s">
         <v>808</v>
@@ -18165,7 +18165,7 @@
         <v>763</v>
       </c>
       <c r="G108" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H108" t="s">
         <v>783</v>
@@ -18192,7 +18192,7 @@
         <v>4</v>
       </c>
       <c r="P108" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="Q108" t="s">
         <v>808</v>
@@ -18278,7 +18278,7 @@
         <v>763</v>
       </c>
       <c r="G109" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H109" t="s">
         <v>782</v>
@@ -18305,7 +18305,7 @@
         <v>4</v>
       </c>
       <c r="P109" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q109" t="s">
         <v>808</v>
@@ -18391,7 +18391,7 @@
         <v>763</v>
       </c>
       <c r="G110" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H110" t="s">
         <v>783</v>
@@ -18418,7 +18418,7 @@
         <v>4</v>
       </c>
       <c r="P110" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="Q110" t="s">
         <v>808</v>
@@ -18504,7 +18504,7 @@
         <v>763</v>
       </c>
       <c r="G111" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H111" t="s">
         <v>782</v>
@@ -18531,7 +18531,7 @@
         <v>4</v>
       </c>
       <c r="P111" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q111" t="s">
         <v>808</v>
@@ -18620,7 +18620,7 @@
         <v>763</v>
       </c>
       <c r="G112" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H112" t="s">
         <v>783</v>
@@ -18647,7 +18647,7 @@
         <v>4</v>
       </c>
       <c r="P112" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="Q112" t="s">
         <v>809</v>
@@ -18733,7 +18733,7 @@
         <v>763</v>
       </c>
       <c r="G113" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H113" t="s">
         <v>778</v>
@@ -18760,7 +18760,7 @@
         <v>4</v>
       </c>
       <c r="P113" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q113" t="s">
         <v>808</v>
@@ -18846,7 +18846,7 @@
         <v>763</v>
       </c>
       <c r="G114" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H114" t="s">
         <v>778</v>
@@ -18873,7 +18873,7 @@
         <v>4</v>
       </c>
       <c r="P114" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q114" t="s">
         <v>809</v>
@@ -18947,7 +18947,7 @@
         <v>763</v>
       </c>
       <c r="G115" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H115" t="s">
         <v>778</v>
@@ -18974,7 +18974,7 @@
         <v>4</v>
       </c>
       <c r="P115" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q115" t="s">
         <v>809</v>
@@ -19051,7 +19051,7 @@
         <v>763</v>
       </c>
       <c r="G116" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H116" t="s">
         <v>778</v>
@@ -19078,7 +19078,7 @@
         <v>4</v>
       </c>
       <c r="P116" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q116" t="s">
         <v>809</v>
@@ -19155,7 +19155,7 @@
         <v>763</v>
       </c>
       <c r="G117" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H117" t="s">
         <v>778</v>
@@ -19182,7 +19182,7 @@
         <v>4</v>
       </c>
       <c r="P117" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="Q117" t="s">
         <v>809</v>
@@ -19289,7 +19289,7 @@
         <v>4</v>
       </c>
       <c r="P118" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q118" t="s">
         <v>810</v>
@@ -19402,7 +19402,7 @@
         <v>4</v>
       </c>
       <c r="P119" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q119" t="s">
         <v>810</v>
@@ -19515,7 +19515,7 @@
         <v>4</v>
       </c>
       <c r="P120" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q120" t="s">
         <v>810</v>
@@ -19631,7 +19631,7 @@
         <v>4</v>
       </c>
       <c r="P121" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q121" t="s">
         <v>810</v>
@@ -19744,7 +19744,7 @@
         <v>4</v>
       </c>
       <c r="P122" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q122" t="s">
         <v>810</v>
@@ -19845,7 +19845,7 @@
         <v>4</v>
       </c>
       <c r="P123" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q123" t="s">
         <v>811</v>
@@ -19958,7 +19958,7 @@
         <v>4</v>
       </c>
       <c r="P124" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q124" t="s">
         <v>811</v>
@@ -20071,7 +20071,7 @@
         <v>4</v>
       </c>
       <c r="P125" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q125" t="s">
         <v>811</v>
@@ -20184,7 +20184,7 @@
         <v>4</v>
       </c>
       <c r="P126" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="Q126" t="s">
         <v>810</v>
@@ -20291,7 +20291,7 @@
         <v>4</v>
       </c>
       <c r="P127" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q127" t="s">
         <v>811</v>
@@ -20401,7 +20401,7 @@
         <v>4</v>
       </c>
       <c r="P128" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q128" t="s">
         <v>810</v>
@@ -20511,7 +20511,7 @@
         <v>4</v>
       </c>
       <c r="P129" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q129" t="s">
         <v>810</v>
@@ -20621,7 +20621,7 @@
         <v>4</v>
       </c>
       <c r="P130" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q130" t="s">
         <v>810</v>
@@ -20731,7 +20731,7 @@
         <v>4</v>
       </c>
       <c r="P131" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="Q131" t="s">
         <v>810</v>
@@ -20829,7 +20829,7 @@
         <v>4</v>
       </c>
       <c r="P132" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q132" t="s">
         <v>810</v>
@@ -20942,7 +20942,7 @@
         <v>4</v>
       </c>
       <c r="P133" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q133" t="s">
         <v>810</v>
@@ -21052,7 +21052,7 @@
         <v>4</v>
       </c>
       <c r="P134" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q134" t="s">
         <v>810</v>
@@ -21156,7 +21156,7 @@
         <v>4</v>
       </c>
       <c r="P135" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q135" t="s">
         <v>811</v>
@@ -21269,7 +21269,7 @@
         <v>4</v>
       </c>
       <c r="P136" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q136" t="s">
         <v>811</v>
@@ -21379,7 +21379,7 @@
         <v>4</v>
       </c>
       <c r="P137" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q137" t="s">
         <v>811</v>
@@ -21495,7 +21495,7 @@
         <v>4</v>
       </c>
       <c r="P138" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q138" t="s">
         <v>811</v>
@@ -21602,7 +21602,7 @@
         <v>4</v>
       </c>
       <c r="P139" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q139" t="s">
         <v>812</v>
@@ -21715,7 +21715,7 @@
         <v>4</v>
       </c>
       <c r="P140" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q140" t="s">
         <v>813</v>
@@ -21831,7 +21831,7 @@
         <v>4</v>
       </c>
       <c r="P141" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q141" t="s">
         <v>813</v>
@@ -21944,7 +21944,7 @@
         <v>4</v>
       </c>
       <c r="P142" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q142" t="s">
         <v>813</v>
@@ -22060,7 +22060,7 @@
         <v>4</v>
       </c>
       <c r="P143" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q143" t="s">
         <v>813</v>
@@ -22173,7 +22173,7 @@
         <v>4</v>
       </c>
       <c r="P144" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q144" t="s">
         <v>813</v>
@@ -22280,7 +22280,7 @@
         <v>4</v>
       </c>
       <c r="P145" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q145" t="s">
         <v>814</v>
@@ -22393,7 +22393,7 @@
         <v>4</v>
       </c>
       <c r="P146" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q146" t="s">
         <v>814</v>
@@ -22506,7 +22506,7 @@
         <v>4</v>
       </c>
       <c r="P147" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q147" t="s">
         <v>812</v>
@@ -22610,7 +22610,7 @@
         <v>4</v>
       </c>
       <c r="P148" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q148" t="s">
         <v>814</v>
@@ -22714,7 +22714,7 @@
         <v>4</v>
       </c>
       <c r="P149" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q149" t="s">
         <v>815</v>
@@ -22830,7 +22830,7 @@
         <v>4</v>
       </c>
       <c r="P150" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q150" t="s">
         <v>815</v>
@@ -22946,7 +22946,7 @@
         <v>4</v>
       </c>
       <c r="P151" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q151" t="s">
         <v>815</v>
@@ -23062,7 +23062,7 @@
         <v>4</v>
       </c>
       <c r="P152" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q152" t="s">
         <v>816</v>
@@ -23175,7 +23175,7 @@
         <v>4</v>
       </c>
       <c r="P153" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q153" t="s">
         <v>813</v>
@@ -23273,7 +23273,7 @@
         <v>4</v>
       </c>
       <c r="P154" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q154" t="s">
         <v>817</v>
@@ -23374,7 +23374,7 @@
         <v>4</v>
       </c>
       <c r="P155" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q155" t="s">
         <v>816</v>
@@ -23490,7 +23490,7 @@
         <v>4</v>
       </c>
       <c r="P156" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q156" t="s">
         <v>813</v>
@@ -23603,7 +23603,7 @@
         <v>4</v>
       </c>
       <c r="P157" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q157" t="s">
         <v>814</v>
@@ -23719,7 +23719,7 @@
         <v>4</v>
       </c>
       <c r="P158" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q158" t="s">
         <v>814</v>
@@ -23823,7 +23823,7 @@
         <v>4</v>
       </c>
       <c r="P159" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q159" t="s">
         <v>815</v>
@@ -23936,7 +23936,7 @@
         <v>4</v>
       </c>
       <c r="P160" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q160" t="s">
         <v>815</v>
@@ -24052,7 +24052,7 @@
         <v>4</v>
       </c>
       <c r="P161" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q161" t="s">
         <v>815</v>
@@ -24168,7 +24168,7 @@
         <v>4</v>
       </c>
       <c r="P162" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q162" t="s">
         <v>816</v>
@@ -24284,7 +24284,7 @@
         <v>4</v>
       </c>
       <c r="P163" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q163" t="s">
         <v>816</v>
@@ -24400,7 +24400,7 @@
         <v>4</v>
       </c>
       <c r="P164" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q164" t="s">
         <v>815</v>
@@ -24510,7 +24510,7 @@
         <v>4</v>
       </c>
       <c r="P165" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q165" t="s">
         <v>818</v>
@@ -24620,7 +24620,7 @@
         <v>790</v>
       </c>
       <c r="P166" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q166" t="s">
         <v>815</v>
@@ -24715,7 +24715,7 @@
         <v>4</v>
       </c>
       <c r="P167" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q167" t="s">
         <v>816</v>
@@ -24831,7 +24831,7 @@
         <v>4</v>
       </c>
       <c r="P168" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q168" t="s">
         <v>816</v>
@@ -24944,7 +24944,7 @@
         <v>4</v>
       </c>
       <c r="P169" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="Q169" t="s">
         <v>819</v>
@@ -25054,7 +25054,7 @@
         <v>4</v>
       </c>
       <c r="P170" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="Q170" t="s">
         <v>819</v>
@@ -25164,7 +25164,7 @@
         <v>4</v>
       </c>
       <c r="P171" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="Q171" t="s">
         <v>819</v>
@@ -25274,7 +25274,7 @@
         <v>4</v>
       </c>
       <c r="P172" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q172" t="s">
         <v>819</v>
@@ -25384,7 +25384,7 @@
         <v>4</v>
       </c>
       <c r="P173" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q173" t="s">
         <v>820</v>
@@ -25488,7 +25488,7 @@
         <v>4</v>
       </c>
       <c r="P174" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="Q174" t="s">
         <v>820</v>
@@ -25586,7 +25586,7 @@
         <v>4</v>
       </c>
       <c r="P175" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q175" t="s">
         <v>813</v>
@@ -25699,7 +25699,7 @@
         <v>4</v>
       </c>
       <c r="P176" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q176" t="s">
         <v>813</v>
@@ -25812,7 +25812,7 @@
         <v>4</v>
       </c>
       <c r="P177" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q177" t="s">
         <v>813</v>
@@ -25925,7 +25925,7 @@
         <v>4</v>
       </c>
       <c r="P178" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q178" t="s">
         <v>813</v>
@@ -26041,7 +26041,7 @@
         <v>4</v>
       </c>
       <c r="P179" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q179" t="s">
         <v>813</v>
@@ -26157,7 +26157,7 @@
         <v>4</v>
       </c>
       <c r="P180" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="Q180" t="s">
         <v>814</v>
@@ -26258,7 +26258,7 @@
         <v>4</v>
       </c>
       <c r="P181" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="Q181" t="s">
         <v>814</v>
